--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo_2.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo_2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="365">
   <si>
     <t>该投资者是否属于本行</t>
   </si>
@@ -1248,15 +1248,19 @@
     <t>34 SPV登记编码</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
+  <si>
+    <t>*投资者分类</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1468,7 +1472,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1540,6 +1544,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1823,8 +1829,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W4"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:X34"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21" style="21" customWidth="1"/>
     <col min="2" max="2" width="23.25" style="21" customWidth="1"/>
@@ -1837,10 +1843,11 @@
     <col min="15" max="15" width="31" style="21" customWidth="1"/>
     <col min="16" max="16" width="26.875" style="21" customWidth="1"/>
     <col min="17" max="23" width="21" style="21" customWidth="1"/>
-    <col min="24" max="16384" width="8.875" style="23"/>
+    <col min="24" max="24" width="19" style="28" customWidth="1"/>
+    <col min="25" max="16384" width="8.875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="13.5" customHeight="1">
       <c r="A1" s="24" t="s">
         <v>346</v>
       </c>
@@ -1910,8 +1917,11 @@
       <c r="W1" s="24" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X1" s="24" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -1934,13 +1944,108 @@
       <c r="U2" s="22"/>
       <c r="V2" s="25"/>
       <c r="W2" s="22"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X2" s="27"/>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="X3" s="27"/>
+    </row>
+    <row r="4" spans="1:24">
       <c r="J4" s="22"/>
+      <c r="X4" s="27"/>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="X5" s="27"/>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="X6" s="27"/>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="X7" s="27"/>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="X8" s="27"/>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="X9" s="27"/>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="X10" s="27"/>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="X11" s="27"/>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="X12" s="27"/>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="X13" s="27"/>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="X14" s="27"/>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="X15" s="27"/>
+    </row>
+    <row r="16" spans="1:24">
+      <c r="X16" s="27"/>
+    </row>
+    <row r="17" spans="24:24">
+      <c r="X17" s="27"/>
+    </row>
+    <row r="18" spans="24:24">
+      <c r="X18" s="27"/>
+    </row>
+    <row r="19" spans="24:24">
+      <c r="X19" s="27"/>
+    </row>
+    <row r="20" spans="24:24">
+      <c r="X20" s="27"/>
+    </row>
+    <row r="21" spans="24:24">
+      <c r="X21" s="27"/>
+    </row>
+    <row r="22" spans="24:24">
+      <c r="X22" s="27"/>
+    </row>
+    <row r="23" spans="24:24">
+      <c r="X23" s="27"/>
+    </row>
+    <row r="24" spans="24:24">
+      <c r="X24" s="27"/>
+    </row>
+    <row r="25" spans="24:24">
+      <c r="X25" s="27"/>
+    </row>
+    <row r="26" spans="24:24">
+      <c r="X26" s="27"/>
+    </row>
+    <row r="27" spans="24:24">
+      <c r="X27" s="27"/>
+    </row>
+    <row r="28" spans="24:24">
+      <c r="X28" s="27"/>
+    </row>
+    <row r="29" spans="24:24">
+      <c r="X29" s="27"/>
+    </row>
+    <row r="30" spans="24:24">
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="24:24">
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="24:24">
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="24:24">
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="24:24">
+      <c r="X34" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
-  <dataValidations count="10">
+  <dataValidations count="11">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576">
       <formula1>"00 居民身份证,01 临时居民身份证,02 户口簿,10 军官证,11 警官证,12 文职干部证,13 士兵证,14 军事院校学员证,15 离休干部荣誉证,16 军官退休证,17 文职干部退休证,20 中华人民共和国护照,21 外国护照,22 港澳往来内地通行证,23 台湾往来内地通行证,24 外国人永久居留证,99 其他"</formula1>
     </dataValidation>
@@ -1971,6 +2076,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576">
       <formula1>"01 保守型,02 稳健型,03 平衡型,04 成长型,05 进取型"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
+      <formula1>"02 合格投资者,01 不特定社会公众"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1980,1693 +2088,1693 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A340"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="82.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="48" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="37.5" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="23.25" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="21" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1">
       <c r="A5" s="8"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1">
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1">
       <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1">
       <c r="A8" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1">
       <c r="A9" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1">
       <c r="A10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1">
       <c r="A11" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1">
       <c r="A12" s="12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1">
       <c r="A13" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1">
       <c r="A14" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1">
       <c r="A15" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1">
       <c r="A16" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1">
       <c r="A17" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1">
       <c r="A18" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1">
       <c r="A19" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1">
       <c r="A22" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1">
       <c r="A23" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1">
       <c r="A24" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1">
       <c r="A25" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1">
       <c r="A26" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1">
       <c r="A27" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1">
       <c r="A28" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1">
       <c r="A29" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1">
       <c r="A30" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1">
       <c r="A31" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1">
       <c r="A32" s="11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1">
       <c r="A33" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1">
       <c r="A34" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1">
       <c r="A35" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1">
       <c r="A36" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1">
       <c r="A37" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1">
       <c r="A38" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1">
       <c r="A39" s="11" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1">
       <c r="A40" s="11" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1">
       <c r="A41" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1">
       <c r="A42" s="16"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1">
       <c r="A43" s="17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1">
       <c r="A44" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1">
       <c r="A45" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1">
       <c r="A46" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1">
       <c r="A47" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1">
       <c r="A48" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1">
       <c r="A49" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1">
       <c r="A50" s="11" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1">
       <c r="A51" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1">
       <c r="A52" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1">
       <c r="A53" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1">
       <c r="A54" s="11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1">
       <c r="A55" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1">
       <c r="A56" s="11" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1">
       <c r="A57" s="11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1">
       <c r="A58" s="11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1">
       <c r="A59" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1">
       <c r="A60" s="11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1">
       <c r="A61" s="11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1">
       <c r="A62" s="11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1">
       <c r="A63" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1">
       <c r="A64" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1">
       <c r="A65" s="11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1">
       <c r="A66" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1">
       <c r="A67" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1">
       <c r="A68" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1">
       <c r="A69" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1">
       <c r="A70" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1">
       <c r="A71" s="15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1">
       <c r="A73" s="17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1">
       <c r="A74" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1">
       <c r="A75" s="19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1">
       <c r="A76" s="19" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1">
       <c r="A77" s="19" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1">
       <c r="A78" s="19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1">
       <c r="A79" s="19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1">
       <c r="A80" s="19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1">
       <c r="A81" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1">
       <c r="A82" s="19" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1">
       <c r="A83" s="19" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1">
       <c r="A84" s="19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1">
       <c r="A85" s="19" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1">
       <c r="A86" s="19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1">
       <c r="A87" s="19" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1">
       <c r="A88" s="19" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1">
       <c r="A89" s="19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1">
       <c r="A90" s="19" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1">
       <c r="A91" s="19" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1">
       <c r="A92" s="19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1">
       <c r="A93" s="19" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1">
       <c r="A94" s="19" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1">
       <c r="A95" s="19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1">
       <c r="A96" s="19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1">
       <c r="A97" s="19" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1">
       <c r="A98" s="19" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1">
       <c r="A99" s="20" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1">
       <c r="A101" s="17" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1">
       <c r="A102" s="18" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1">
       <c r="A103" s="19" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1">
       <c r="A104" s="19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1">
       <c r="A105" s="19" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1">
       <c r="A106" s="19" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1">
       <c r="A107" s="19" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1">
       <c r="A108" s="19" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1">
       <c r="A109" s="19" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1">
       <c r="A110" s="19" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1">
       <c r="A111" s="19" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1">
       <c r="A112" s="19" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1">
       <c r="A113" s="19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1">
       <c r="A114" s="19" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1">
       <c r="A115" s="19" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1">
       <c r="A116" s="19" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1">
       <c r="A117" s="19" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1">
       <c r="A118" s="19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1">
       <c r="A119" s="19" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1">
       <c r="A120" s="19" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1">
       <c r="A121" s="19" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1">
       <c r="A122" s="19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1">
       <c r="A123" s="19" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1">
       <c r="A124" s="19" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1">
       <c r="A125" s="19" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:1">
       <c r="A126" s="19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:1">
       <c r="A127" s="19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:1">
       <c r="A128" s="19" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:1">
       <c r="A129" s="19" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:1">
       <c r="A130" s="19" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:1">
       <c r="A131" s="19" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:1">
       <c r="A132" s="19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:1">
       <c r="A133" s="19" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:1">
       <c r="A134" s="19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:1">
       <c r="A135" s="19" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:1">
       <c r="A136" s="19" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:1">
       <c r="A137" s="19" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:1">
       <c r="A138" s="19" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:1">
       <c r="A139" s="19" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:1">
       <c r="A140" s="19" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:1">
       <c r="A141" s="19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:1">
       <c r="A142" s="19" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:1">
       <c r="A143" s="19" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:1">
       <c r="A144" s="19" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:1">
       <c r="A145" s="19" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:1">
       <c r="A146" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:1">
       <c r="A147" s="19" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:1">
       <c r="A148" s="19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:1">
       <c r="A149" s="19" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:1">
       <c r="A150" s="19" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:1">
       <c r="A151" s="19" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:1">
       <c r="A152" s="19" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:1">
       <c r="A153" s="19" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:1">
       <c r="A154" s="19" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:1">
       <c r="A155" s="19" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:1">
       <c r="A156" s="19" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:1">
       <c r="A157" s="19" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:1">
       <c r="A158" s="19" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:1">
       <c r="A159" s="19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:1">
       <c r="A160" s="19" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:1">
       <c r="A161" s="19" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:1">
       <c r="A162" s="19" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:1">
       <c r="A163" s="19" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:1">
       <c r="A164" s="19" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:1">
       <c r="A165" s="19" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:1">
       <c r="A166" s="19" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:1">
       <c r="A167" s="19" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:1">
       <c r="A168" s="19" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:1">
       <c r="A169" s="19" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:1">
       <c r="A170" s="19" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:1">
       <c r="A171" s="19" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:1">
       <c r="A172" s="19" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:1">
       <c r="A173" s="19" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:1">
       <c r="A174" s="19" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:1">
       <c r="A175" s="19" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:1">
       <c r="A176" s="19" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:1">
       <c r="A177" s="19" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:1">
       <c r="A178" s="19" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:1">
       <c r="A179" s="19" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:1">
       <c r="A180" s="19" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:1">
       <c r="A181" s="19" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:1">
       <c r="A182" s="19" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:1">
       <c r="A183" s="19" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:1">
       <c r="A184" s="19" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:1">
       <c r="A185" s="19" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:1">
       <c r="A186" s="19" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:1">
       <c r="A187" s="19" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:1">
       <c r="A188" s="19" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:1">
       <c r="A189" s="19" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:1">
       <c r="A190" s="19" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:1">
       <c r="A191" s="19" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:1">
       <c r="A192" s="19" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:1">
       <c r="A193" s="19" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:1">
       <c r="A194" s="19" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:1">
       <c r="A195" s="19" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:1">
       <c r="A196" s="19" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:1">
       <c r="A197" s="19" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:1">
       <c r="A198" s="19" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:1">
       <c r="A199" s="19" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:1">
       <c r="A200" s="19" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:1">
       <c r="A201" s="19" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:1">
       <c r="A202" s="19" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:1">
       <c r="A203" s="19" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:1">
       <c r="A204" s="19" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:1">
       <c r="A205" s="19" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:1">
       <c r="A206" s="19" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:1">
       <c r="A207" s="19" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:1">
       <c r="A208" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:1">
       <c r="A209" s="19" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:1">
       <c r="A210" s="19" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:1">
       <c r="A211" s="19" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:1">
       <c r="A212" s="19" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:1">
       <c r="A213" s="19" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:1">
       <c r="A214" s="19" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:1">
       <c r="A215" s="19" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:1">
       <c r="A216" s="19" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:1">
       <c r="A217" s="19" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:1">
       <c r="A218" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:1">
       <c r="A219" s="19" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:1">
       <c r="A220" s="19" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:1">
       <c r="A221" s="19" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:1">
       <c r="A222" s="19" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:1">
       <c r="A223" s="19" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:1">
       <c r="A224" s="19" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:1">
       <c r="A225" s="19" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:1">
       <c r="A226" s="19" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:1">
       <c r="A227" s="19" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:1">
       <c r="A228" s="19" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:1">
       <c r="A229" s="19" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:1">
       <c r="A230" s="19" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:1">
       <c r="A231" s="19" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:1">
       <c r="A232" s="19" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:1">
       <c r="A233" s="19" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:1">
       <c r="A234" s="19" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:1">
       <c r="A235" s="19" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:1">
       <c r="A236" s="19" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:1">
       <c r="A237" s="19" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:1">
       <c r="A238" s="19" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:1">
       <c r="A239" s="19" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:1">
       <c r="A240" s="19" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:1">
       <c r="A241" s="19" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:1">
       <c r="A242" s="19" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:1">
       <c r="A243" s="19" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:1">
       <c r="A244" s="19" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:1">
       <c r="A245" s="19" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:1">
       <c r="A246" s="19" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:1">
       <c r="A247" s="19" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:1">
       <c r="A248" s="19" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:1">
       <c r="A249" s="19" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:1">
       <c r="A250" s="19" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:1">
       <c r="A251" s="19" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:1">
       <c r="A252" s="19" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:1">
       <c r="A253" s="19" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:1">
       <c r="A254" s="19" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:1">
       <c r="A255" s="19" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:1">
       <c r="A256" s="19" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:1">
       <c r="A257" s="19" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:1">
       <c r="A258" s="19" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:1">
       <c r="A259" s="19" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:1">
       <c r="A260" s="19" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:1">
       <c r="A261" s="19" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:1">
       <c r="A262" s="19" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:1">
       <c r="A263" s="19" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:1">
       <c r="A264" s="19" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:1">
       <c r="A265" s="19" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:1">
       <c r="A266" s="19" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:1">
       <c r="A267" s="19" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:1">
       <c r="A268" s="19" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:1">
       <c r="A269" s="19" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:1">
       <c r="A270" s="19" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:1">
       <c r="A271" s="19" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:1">
       <c r="A272" s="19" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:1">
       <c r="A273" s="19" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:1">
       <c r="A274" s="19" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:1">
       <c r="A275" s="19" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:1">
       <c r="A276" s="19" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:1">
       <c r="A277" s="19" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:1">
       <c r="A278" s="19" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:1">
       <c r="A279" s="19" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:1">
       <c r="A280" s="19" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:1">
       <c r="A281" s="19" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:1">
       <c r="A282" s="19" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:1">
       <c r="A283" s="19" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:1">
       <c r="A284" s="19" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:1">
       <c r="A285" s="19" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:1">
       <c r="A286" s="19" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:1">
       <c r="A287" s="19" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:1">
       <c r="A288" s="19" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:1">
       <c r="A289" s="19" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:1">
       <c r="A290" s="19" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:1">
       <c r="A291" s="19" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:1">
       <c r="A292" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:1">
       <c r="A293" s="19" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:1">
       <c r="A294" s="19" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:1">
       <c r="A295" s="19" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:1">
       <c r="A296" s="19" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:1">
       <c r="A297" s="19" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:1">
       <c r="A298" s="19" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:1">
       <c r="A299" s="19" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:1">
       <c r="A300" s="19" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:1">
       <c r="A301" s="19" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:1">
       <c r="A302" s="19" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:1">
       <c r="A303" s="19" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:1">
       <c r="A304" s="19" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:1">
       <c r="A305" s="19" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:1">
       <c r="A306" s="19" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:1">
       <c r="A307" s="19" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:1">
       <c r="A308" s="19" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:1">
       <c r="A309" s="19" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:1">
       <c r="A310" s="19" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:1">
       <c r="A311" s="19" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:1">
       <c r="A312" s="19" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:1">
       <c r="A313" s="19" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:1">
       <c r="A314" s="19" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:1">
       <c r="A315" s="19" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:1">
       <c r="A316" s="19" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:1">
       <c r="A317" s="19" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:1">
       <c r="A318" s="19" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:1">
       <c r="A319" s="19" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:1">
       <c r="A320" s="19" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:1">
       <c r="A321" s="19" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:1">
       <c r="A322" s="19" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:1">
       <c r="A323" s="19" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:1">
       <c r="A324" s="19" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:1">
       <c r="A325" s="19" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:1">
       <c r="A326" s="19" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:1">
       <c r="A327" s="19" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:1">
       <c r="A328" s="19" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:1">
       <c r="A329" s="19" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:1">
       <c r="A330" s="19" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:1">
       <c r="A331" s="19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:1">
       <c r="A332" s="19" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:1">
       <c r="A333" s="19" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:1">
       <c r="A334" s="19" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:1">
       <c r="A335" s="19" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:1">
       <c r="A336" s="19" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:1">
       <c r="A337" s="19" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:1">
       <c r="A338" s="19" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:1">
       <c r="A339" s="19" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:1">
       <c r="A340" s="20" t="s">
         <v>337</v>
       </c>
@@ -3681,12 +3789,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="52.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>338</v>
       </c>
@@ -3694,7 +3802,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>340</v>
       </c>
@@ -3702,7 +3810,7 @@
         <v>43250</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="71.25">
       <c r="A3" s="5" t="s">
         <v>341</v>
       </c>
